--- a/volunteer_application_forms/043_crisis_response_team_application_form--volunteer_application_forms.xlsx
+++ b/volunteer_application_forms/043_crisis_response_team_application_form--volunteer_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1079,8 +1079,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'crisis_response_team'}</t>
+          <t>crisis_response_team</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Crisis Response Team'}</t>
+          <t>Crisis Response Team</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'support_services'}</t>
+          <t>support_services</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Support Services'}</t>
+          <t>Support Services</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'crisis_response'}</t>
+          <t>crisis_response</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Crisis Response'}</t>
+          <t>Crisis Response</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'support'}</t>
+          <t>support</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Support'}</t>
+          <t>Support</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'american_red_cross'}</t>
+          <t>american_red_cross</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'American Red Cross'}</t>
+          <t>American Red Cross</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'red_cross'}</t>
+          <t>red_cross</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Red Cross'}</t>
+          <t>Red Cross</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'college'}</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'College'}</t>
+          <t>College</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
